--- a/Configs/GameConfig/Datas/global.xlsx
+++ b/Configs/GameConfig/Datas/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20625" windowHeight="6645"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>##column#var</t>
   </si>
@@ -54,6 +54,18 @@
   </si>
   <si>
     <t>最大背包容量</t>
+  </si>
+  <si>
+    <t>MaxStamina</t>
+  </si>
+  <si>
+    <t>最大体力</t>
+  </si>
+  <si>
+    <t>MaxStress</t>
+  </si>
+  <si>
+    <t>最大压力</t>
   </si>
 </sst>
 </file>
@@ -1005,8 +1017,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
+  <dimension ref="A1:X5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="19.625" customWidth="1"/>
     <col min="2" max="5" width="16.5" customWidth="1"/>
@@ -1090,6 +1102,34 @@
         <v>8</v>
       </c>
     </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/global.xlsx
+++ b/Configs/GameConfig/Datas/global.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>##column#var</t>
   </si>
@@ -66,6 +66,15 @@
   </si>
   <si>
     <t>最大压力</t>
+  </si>
+  <si>
+    <t>CharacterId_My</t>
+  </si>
+  <si>
+    <t>CharacterId_ErGou</t>
+  </si>
+  <si>
+    <t>CharacterId_CuiHua</t>
   </si>
 </sst>
 </file>
@@ -694,10 +703,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1017,25 +1032,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:X8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="19.625" customWidth="1"/>
-    <col min="2" max="5" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="14.875" style="2" customWidth="1"/>
+    <col min="4" max="5" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:24">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="4"/>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F1"/>
@@ -1059,13 +1076,13 @@
       <c r="X1"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:24">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F2"/>
@@ -1095,7 +1112,7 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>10</v>
       </c>
       <c r="E3" t="s">
@@ -1109,7 +1126,7 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>100</v>
       </c>
       <c r="E4" t="s">
@@ -1123,11 +1140,44 @@
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
